--- a/Google_DSA_Interview_Prep.xlsx
+++ b/Google_DSA_Interview_Prep.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MaitySom\Desktop\Somneel\Somneel_Maity\K_Tech\DSA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hp-my.sharepoint.com/personal/somneel_maity_hp_com/Documents/Desktop/Somneel/Somneel_Maity/DSA-and-CP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD68C9B-D7B9-4154-8CF7-2207830BE070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{1FD68C9B-D7B9-4154-8CF7-2207830BE070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12F78771-7DDE-4328-96FB-8BF54C873FBE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="759">
   <si>
     <t>Google DSA Interview Prep — Overview</t>
   </si>
@@ -3497,8 +3497,8 @@
       <c r="F4" s="31" t="s">
         <v>469</v>
       </c>
-      <c r="G4" s="32" t="s">
-        <v>63</v>
+      <c r="G4" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3520,8 +3520,8 @@
       <c r="F5" s="31" t="s">
         <v>472</v>
       </c>
-      <c r="G5" s="32" t="s">
-        <v>63</v>
+      <c r="G5" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3543,8 +3543,8 @@
       <c r="F6" s="31" t="s">
         <v>475</v>
       </c>
-      <c r="G6" s="32" t="s">
-        <v>63</v>
+      <c r="G6" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3566,8 +3566,8 @@
       <c r="F7" s="31" t="s">
         <v>478</v>
       </c>
-      <c r="G7" s="32" t="s">
-        <v>63</v>
+      <c r="G7" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3589,8 +3589,8 @@
       <c r="F8" s="31" t="s">
         <v>481</v>
       </c>
-      <c r="G8" s="32" t="s">
-        <v>63</v>
+      <c r="G8" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3612,8 +3612,8 @@
       <c r="F9" s="35" t="s">
         <v>484</v>
       </c>
-      <c r="G9" s="36" t="s">
-        <v>63</v>
+      <c r="G9" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3635,8 +3635,8 @@
       <c r="F10" s="35" t="s">
         <v>487</v>
       </c>
-      <c r="G10" s="36" t="s">
-        <v>63</v>
+      <c r="G10" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3658,8 +3658,8 @@
       <c r="F11" s="35" t="s">
         <v>490</v>
       </c>
-      <c r="G11" s="36" t="s">
-        <v>63</v>
+      <c r="G11" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3681,8 +3681,8 @@
       <c r="F12" s="31" t="s">
         <v>493</v>
       </c>
-      <c r="G12" s="32" t="s">
-        <v>63</v>
+      <c r="G12" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3704,8 +3704,8 @@
       <c r="F13" s="35" t="s">
         <v>496</v>
       </c>
-      <c r="G13" s="36" t="s">
-        <v>63</v>
+      <c r="G13" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3727,8 +3727,8 @@
       <c r="F14" s="31" t="s">
         <v>499</v>
       </c>
-      <c r="G14" s="32" t="s">
-        <v>63</v>
+      <c r="G14" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3750,8 +3750,8 @@
       <c r="F15" s="35" t="s">
         <v>502</v>
       </c>
-      <c r="G15" s="36" t="s">
-        <v>63</v>
+      <c r="G15" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3773,8 +3773,8 @@
       <c r="F16" s="35" t="s">
         <v>505</v>
       </c>
-      <c r="G16" s="36" t="s">
-        <v>63</v>
+      <c r="G16" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3796,8 +3796,8 @@
       <c r="F17" s="31" t="s">
         <v>508</v>
       </c>
-      <c r="G17" s="32" t="s">
-        <v>63</v>
+      <c r="G17" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3904,8 +3904,8 @@
       <c r="F4" s="35" t="s">
         <v>513</v>
       </c>
-      <c r="G4" s="36" t="s">
-        <v>63</v>
+      <c r="G4" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3927,8 +3927,8 @@
       <c r="F5" s="35" t="s">
         <v>514</v>
       </c>
-      <c r="G5" s="36" t="s">
-        <v>63</v>
+      <c r="G5" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3950,8 +3950,8 @@
       <c r="F6" s="31" t="s">
         <v>517</v>
       </c>
-      <c r="G6" s="32" t="s">
-        <v>63</v>
+      <c r="G6" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3973,8 +3973,8 @@
       <c r="F7" s="31" t="s">
         <v>518</v>
       </c>
-      <c r="G7" s="32" t="s">
-        <v>63</v>
+      <c r="G7" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -3996,8 +3996,8 @@
       <c r="F8" s="31" t="s">
         <v>521</v>
       </c>
-      <c r="G8" s="32" t="s">
-        <v>63</v>
+      <c r="G8" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4019,8 +4019,8 @@
       <c r="F9" s="31" t="s">
         <v>524</v>
       </c>
-      <c r="G9" s="32" t="s">
-        <v>63</v>
+      <c r="G9" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4042,8 +4042,8 @@
       <c r="F10" s="35" t="s">
         <v>527</v>
       </c>
-      <c r="G10" s="36" t="s">
-        <v>63</v>
+      <c r="G10" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4065,8 +4065,8 @@
       <c r="F11" s="35" t="s">
         <v>193</v>
       </c>
-      <c r="G11" s="36" t="s">
-        <v>63</v>
+      <c r="G11" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4088,8 +4088,8 @@
       <c r="F12" s="31" t="s">
         <v>530</v>
       </c>
-      <c r="G12" s="32" t="s">
-        <v>63</v>
+      <c r="G12" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4111,8 +4111,8 @@
       <c r="F13" s="31" t="s">
         <v>533</v>
       </c>
-      <c r="G13" s="32" t="s">
-        <v>63</v>
+      <c r="G13" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4134,8 +4134,8 @@
       <c r="F14" s="31" t="s">
         <v>536</v>
       </c>
-      <c r="G14" s="32" t="s">
-        <v>63</v>
+      <c r="G14" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4157,8 +4157,8 @@
       <c r="F15" s="35" t="s">
         <v>539</v>
       </c>
-      <c r="G15" s="36" t="s">
-        <v>63</v>
+      <c r="G15" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4180,8 +4180,8 @@
       <c r="F16" s="31" t="s">
         <v>542</v>
       </c>
-      <c r="G16" s="32" t="s">
-        <v>63</v>
+      <c r="G16" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4203,8 +4203,8 @@
       <c r="F17" s="31" t="s">
         <v>545</v>
       </c>
-      <c r="G17" s="32" t="s">
-        <v>63</v>
+      <c r="G17" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4226,8 +4226,8 @@
       <c r="F18" s="35" t="s">
         <v>548</v>
       </c>
-      <c r="G18" s="36" t="s">
-        <v>63</v>
+      <c r="G18" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4335,8 +4335,8 @@
       <c r="F4" s="31" t="s">
         <v>553</v>
       </c>
-      <c r="G4" s="32" t="s">
-        <v>63</v>
+      <c r="G4" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4358,8 +4358,8 @@
       <c r="F5" s="31" t="s">
         <v>556</v>
       </c>
-      <c r="G5" s="32" t="s">
-        <v>63</v>
+      <c r="G5" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4381,8 +4381,8 @@
       <c r="F6" s="35" t="s">
         <v>557</v>
       </c>
-      <c r="G6" s="36" t="s">
-        <v>63</v>
+      <c r="G6" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4404,8 +4404,8 @@
       <c r="F7" s="31" t="s">
         <v>560</v>
       </c>
-      <c r="G7" s="32" t="s">
-        <v>63</v>
+      <c r="G7" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4427,8 +4427,8 @@
       <c r="F8" s="31" t="s">
         <v>563</v>
       </c>
-      <c r="G8" s="32" t="s">
-        <v>63</v>
+      <c r="G8" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4450,8 +4450,8 @@
       <c r="F9" s="31" t="s">
         <v>566</v>
       </c>
-      <c r="G9" s="32" t="s">
-        <v>63</v>
+      <c r="G9" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4473,8 +4473,8 @@
       <c r="F10" s="35" t="s">
         <v>569</v>
       </c>
-      <c r="G10" s="36" t="s">
-        <v>63</v>
+      <c r="G10" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4643,8 +4643,8 @@
       <c r="F7" s="26" t="s">
         <v>583</v>
       </c>
-      <c r="G7" s="27" t="s">
-        <v>63</v>
+      <c r="G7" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4666,8 +4666,8 @@
       <c r="F8" s="26" t="s">
         <v>586</v>
       </c>
-      <c r="G8" s="27" t="s">
-        <v>63</v>
+      <c r="G8" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4689,8 +4689,8 @@
       <c r="F9" s="31" t="s">
         <v>589</v>
       </c>
-      <c r="G9" s="32" t="s">
-        <v>63</v>
+      <c r="G9" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4712,8 +4712,8 @@
       <c r="F10" s="31" t="s">
         <v>590</v>
       </c>
-      <c r="G10" s="32" t="s">
-        <v>63</v>
+      <c r="G10" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4735,8 +4735,8 @@
       <c r="F11" s="31" t="s">
         <v>593</v>
       </c>
-      <c r="G11" s="32" t="s">
-        <v>63</v>
+      <c r="G11" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4758,8 +4758,8 @@
       <c r="F12" s="31" t="s">
         <v>596</v>
       </c>
-      <c r="G12" s="32" t="s">
-        <v>63</v>
+      <c r="G12" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4781,8 +4781,8 @@
       <c r="F13" s="31" t="s">
         <v>599</v>
       </c>
-      <c r="G13" s="32" t="s">
-        <v>63</v>
+      <c r="G13" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4804,8 +4804,8 @@
       <c r="F14" s="31" t="s">
         <v>602</v>
       </c>
-      <c r="G14" s="32" t="s">
-        <v>63</v>
+      <c r="G14" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4827,8 +4827,8 @@
       <c r="F15" s="31" t="s">
         <v>605</v>
       </c>
-      <c r="G15" s="32" t="s">
-        <v>63</v>
+      <c r="G15" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4850,8 +4850,8 @@
       <c r="F16" s="31" t="s">
         <v>608</v>
       </c>
-      <c r="G16" s="32" t="s">
-        <v>63</v>
+      <c r="G16" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4873,8 +4873,8 @@
       <c r="F17" s="35" t="s">
         <v>611</v>
       </c>
-      <c r="G17" s="36" t="s">
-        <v>63</v>
+      <c r="G17" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4896,8 +4896,8 @@
       <c r="F18" s="31" t="s">
         <v>614</v>
       </c>
-      <c r="G18" s="32" t="s">
-        <v>63</v>
+      <c r="G18" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4919,8 +4919,8 @@
       <c r="F19" s="35" t="s">
         <v>617</v>
       </c>
-      <c r="G19" s="36" t="s">
-        <v>63</v>
+      <c r="G19" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4942,8 +4942,8 @@
       <c r="F20" s="26" t="s">
         <v>620</v>
       </c>
-      <c r="G20" s="27" t="s">
-        <v>63</v>
+      <c r="G20" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4965,8 +4965,8 @@
       <c r="F21" s="31" t="s">
         <v>623</v>
       </c>
-      <c r="G21" s="32" t="s">
-        <v>63</v>
+      <c r="G21" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5077,8 +5077,8 @@
       <c r="F4" s="31" t="s">
         <v>626</v>
       </c>
-      <c r="G4" s="32" t="s">
-        <v>63</v>
+      <c r="G4" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5100,8 +5100,8 @@
       <c r="F5" s="35" t="s">
         <v>629</v>
       </c>
-      <c r="G5" s="36" t="s">
-        <v>63</v>
+      <c r="G5" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5123,8 +5123,8 @@
       <c r="F6" s="35" t="s">
         <v>630</v>
       </c>
-      <c r="G6" s="36" t="s">
-        <v>63</v>
+      <c r="G6" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5146,8 +5146,8 @@
       <c r="F7" s="31" t="s">
         <v>633</v>
       </c>
-      <c r="G7" s="32" t="s">
-        <v>63</v>
+      <c r="G7" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5169,8 +5169,8 @@
       <c r="F8" s="35" t="s">
         <v>634</v>
       </c>
-      <c r="G8" s="36" t="s">
-        <v>63</v>
+      <c r="G8" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5192,8 +5192,8 @@
       <c r="F9" s="31" t="s">
         <v>637</v>
       </c>
-      <c r="G9" s="32" t="s">
-        <v>63</v>
+      <c r="G9" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5215,8 +5215,8 @@
       <c r="F10" s="31" t="s">
         <v>639</v>
       </c>
-      <c r="G10" s="32" t="s">
-        <v>63</v>
+      <c r="G10" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5238,8 +5238,8 @@
       <c r="F11" s="31" t="s">
         <v>642</v>
       </c>
-      <c r="G11" s="32" t="s">
-        <v>63</v>
+      <c r="G11" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5261,8 +5261,8 @@
       <c r="F12" s="31" t="s">
         <v>645</v>
       </c>
-      <c r="G12" s="32" t="s">
-        <v>63</v>
+      <c r="G12" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5284,8 +5284,8 @@
       <c r="F13" s="31" t="s">
         <v>648</v>
       </c>
-      <c r="G13" s="32" t="s">
-        <v>63</v>
+      <c r="G13" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5307,8 +5307,8 @@
       <c r="F14" s="31" t="s">
         <v>650</v>
       </c>
-      <c r="G14" s="32" t="s">
-        <v>63</v>
+      <c r="G14" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5330,8 +5330,8 @@
       <c r="F15" s="26" t="s">
         <v>653</v>
       </c>
-      <c r="G15" s="27" t="s">
-        <v>63</v>
+      <c r="G15" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5353,8 +5353,8 @@
       <c r="F16" s="31" t="s">
         <v>656</v>
       </c>
-      <c r="G16" s="32" t="s">
-        <v>63</v>
+      <c r="G16" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5376,8 +5376,8 @@
       <c r="F17" s="35" t="s">
         <v>657</v>
       </c>
-      <c r="G17" s="36" t="s">
-        <v>63</v>
+      <c r="G17" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6036,8 +6036,8 @@
       <c r="F28" s="35" t="s">
         <v>679</v>
       </c>
-      <c r="G28" s="36" t="s">
-        <v>63</v>
+      <c r="G28" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6059,8 +6059,8 @@
       <c r="F29" s="35" t="s">
         <v>680</v>
       </c>
-      <c r="G29" s="36" t="s">
-        <v>63</v>
+      <c r="G29" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6082,8 +6082,8 @@
       <c r="F30" s="35" t="s">
         <v>681</v>
       </c>
-      <c r="G30" s="36" t="s">
-        <v>63</v>
+      <c r="G30" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6105,8 +6105,8 @@
       <c r="F31" s="35" t="s">
         <v>402</v>
       </c>
-      <c r="G31" s="36" t="s">
-        <v>63</v>
+      <c r="G31" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6128,8 +6128,8 @@
       <c r="F32" s="35" t="s">
         <v>682</v>
       </c>
-      <c r="G32" s="36" t="s">
-        <v>63</v>
+      <c r="G32" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6151,8 +6151,8 @@
       <c r="F33" s="35" t="s">
         <v>683</v>
       </c>
-      <c r="G33" s="36" t="s">
-        <v>63</v>
+      <c r="G33" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6780,7 +6780,7 @@
         <v>85</v>
       </c>
       <c r="G11" s="64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7049,8 +7049,8 @@
       <c r="F4" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="G4" s="32" t="s">
-        <v>63</v>
+      <c r="G4" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7072,8 +7072,8 @@
       <c r="F5" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="G5" s="36" t="s">
-        <v>63</v>
+      <c r="G5" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7095,8 +7095,8 @@
       <c r="F6" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="G6" s="32" t="s">
-        <v>63</v>
+      <c r="G6" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7118,8 +7118,8 @@
       <c r="F7" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="G7" s="32" t="s">
-        <v>63</v>
+      <c r="G7" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7141,8 +7141,8 @@
       <c r="F8" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="G8" s="32" t="s">
-        <v>63</v>
+      <c r="G8" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7164,8 +7164,8 @@
       <c r="F9" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="G9" s="36" t="s">
-        <v>63</v>
+      <c r="G9" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7187,8 +7187,8 @@
       <c r="F10" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="G10" s="32" t="s">
-        <v>63</v>
+      <c r="G10" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7210,8 +7210,8 @@
       <c r="F11" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="G11" s="32" t="s">
-        <v>63</v>
+      <c r="G11" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7233,8 +7233,8 @@
       <c r="F12" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="G12" s="32" t="s">
-        <v>63</v>
+      <c r="G12" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7256,8 +7256,8 @@
       <c r="F13" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="G13" s="36" t="s">
-        <v>63</v>
+      <c r="G13" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7279,8 +7279,8 @@
       <c r="F14" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="G14" s="27" t="s">
-        <v>63</v>
+      <c r="G14" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7302,8 +7302,8 @@
       <c r="F15" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="G15" s="32" t="s">
-        <v>63</v>
+      <c r="G15" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7325,8 +7325,8 @@
       <c r="F16" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="G16" s="32" t="s">
-        <v>63</v>
+      <c r="G16" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7348,8 +7348,8 @@
       <c r="F17" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="G17" s="36" t="s">
-        <v>63</v>
+      <c r="G17" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7371,8 +7371,8 @@
       <c r="F18" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="G18" s="32" t="s">
-        <v>63</v>
+      <c r="G18" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7394,8 +7394,8 @@
       <c r="F19" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="G19" s="36" t="s">
-        <v>63</v>
+      <c r="G19" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7504,8 +7504,8 @@
       <c r="F4" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="G4" s="36" t="s">
-        <v>63</v>
+      <c r="G4" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7527,8 +7527,8 @@
       <c r="F5" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="G5" s="32" t="s">
-        <v>63</v>
+      <c r="G5" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7550,8 +7550,8 @@
       <c r="F6" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="G6" s="32" t="s">
-        <v>63</v>
+      <c r="G6" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7573,8 +7573,8 @@
       <c r="F7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="G7" s="32" t="s">
-        <v>63</v>
+      <c r="G7" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7596,8 +7596,8 @@
       <c r="F8" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="G8" s="32" t="s">
-        <v>63</v>
+      <c r="G8" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7619,8 +7619,8 @@
       <c r="F9" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="G9" s="32" t="s">
-        <v>63</v>
+      <c r="G9" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7642,8 +7642,8 @@
       <c r="F10" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="G10" s="32" t="s">
-        <v>63</v>
+      <c r="G10" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7665,8 +7665,8 @@
       <c r="F11" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="G11" s="32" t="s">
-        <v>63</v>
+      <c r="G11" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7688,8 +7688,8 @@
       <c r="F12" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="G12" s="36" t="s">
-        <v>63</v>
+      <c r="G12" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7711,8 +7711,8 @@
       <c r="F13" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="G13" s="32" t="s">
-        <v>63</v>
+      <c r="G13" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7734,8 +7734,8 @@
       <c r="F14" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="G14" s="32" t="s">
-        <v>63</v>
+      <c r="G14" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7757,8 +7757,8 @@
       <c r="F15" s="35" t="s">
         <v>193</v>
       </c>
-      <c r="G15" s="36" t="s">
-        <v>63</v>
+      <c r="G15" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7863,8 +7863,8 @@
       <c r="F4" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="G4" s="27" t="s">
-        <v>63</v>
+      <c r="G4" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7886,8 +7886,8 @@
       <c r="F5" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="G5" s="32" t="s">
-        <v>63</v>
+      <c r="G5" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7909,8 +7909,8 @@
       <c r="F6" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="G6" s="32" t="s">
-        <v>63</v>
+      <c r="G6" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7932,8 +7932,8 @@
       <c r="F7" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="G7" s="36" t="s">
-        <v>63</v>
+      <c r="G7" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7955,8 +7955,8 @@
       <c r="F8" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="G8" s="36" t="s">
-        <v>63</v>
+      <c r="G8" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7978,8 +7978,8 @@
       <c r="F9" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="G9" s="36" t="s">
-        <v>63</v>
+      <c r="G9" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8001,8 +8001,8 @@
       <c r="F10" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="G10" s="32" t="s">
-        <v>63</v>
+      <c r="G10" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8024,8 +8024,8 @@
       <c r="F11" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="G11" s="32" t="s">
-        <v>63</v>
+      <c r="G11" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8047,8 +8047,8 @@
       <c r="F12" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="G12" s="32" t="s">
-        <v>63</v>
+      <c r="G12" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8070,8 +8070,8 @@
       <c r="F13" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="G13" s="32" t="s">
-        <v>63</v>
+      <c r="G13" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8093,8 +8093,8 @@
       <c r="F14" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="G14" s="32" t="s">
-        <v>63</v>
+      <c r="G14" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8198,8 +8198,8 @@
       <c r="F4" s="26" t="s">
         <v>229</v>
       </c>
-      <c r="G4" s="27" t="s">
-        <v>63</v>
+      <c r="G4" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8221,8 +8221,8 @@
       <c r="F5" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="G5" s="27" t="s">
-        <v>63</v>
+      <c r="G5" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8244,8 +8244,8 @@
       <c r="F6" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="G6" s="27" t="s">
-        <v>63</v>
+      <c r="G6" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8267,8 +8267,8 @@
       <c r="F7" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="G7" s="32" t="s">
-        <v>63</v>
+      <c r="G7" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8290,8 +8290,8 @@
       <c r="F8" s="31" t="s">
         <v>241</v>
       </c>
-      <c r="G8" s="32" t="s">
-        <v>63</v>
+      <c r="G8" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8313,8 +8313,8 @@
       <c r="F9" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="G9" s="32" t="s">
-        <v>63</v>
+      <c r="G9" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8336,8 +8336,8 @@
       <c r="F10" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="G10" s="32" t="s">
-        <v>63</v>
+      <c r="G10" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8359,8 +8359,8 @@
       <c r="F11" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="G11" s="36" t="s">
-        <v>63</v>
+      <c r="G11" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8382,8 +8382,8 @@
       <c r="F12" s="35" t="s">
         <v>253</v>
       </c>
-      <c r="G12" s="36" t="s">
-        <v>63</v>
+      <c r="G12" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8405,8 +8405,8 @@
       <c r="F13" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="G13" s="32" t="s">
-        <v>63</v>
+      <c r="G13" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8428,8 +8428,8 @@
       <c r="F14" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="G14" s="32" t="s">
-        <v>63</v>
+      <c r="G14" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8451,8 +8451,8 @@
       <c r="F15" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="G15" s="27" t="s">
-        <v>63</v>
+      <c r="G15" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8557,8 +8557,8 @@
       <c r="F4" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="G4" s="27" t="s">
-        <v>63</v>
+      <c r="G4" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8580,8 +8580,8 @@
       <c r="F5" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="G5" s="27" t="s">
-        <v>63</v>
+      <c r="G5" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8603,8 +8603,8 @@
       <c r="F6" s="26" t="s">
         <v>273</v>
       </c>
-      <c r="G6" s="27" t="s">
-        <v>63</v>
+      <c r="G6" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8626,8 +8626,8 @@
       <c r="F7" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="G7" s="27" t="s">
-        <v>63</v>
+      <c r="G7" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8649,8 +8649,8 @@
       <c r="F8" s="31" t="s">
         <v>279</v>
       </c>
-      <c r="G8" s="32" t="s">
-        <v>63</v>
+      <c r="G8" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8672,8 +8672,8 @@
       <c r="F9" s="31" t="s">
         <v>282</v>
       </c>
-      <c r="G9" s="32" t="s">
-        <v>63</v>
+      <c r="G9" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8695,8 +8695,8 @@
       <c r="F10" s="31" t="s">
         <v>285</v>
       </c>
-      <c r="G10" s="32" t="s">
-        <v>63</v>
+      <c r="G10" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8718,8 +8718,8 @@
       <c r="F11" s="31" t="s">
         <v>288</v>
       </c>
-      <c r="G11" s="32" t="s">
-        <v>63</v>
+      <c r="G11" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8741,8 +8741,8 @@
       <c r="F12" s="35" t="s">
         <v>291</v>
       </c>
-      <c r="G12" s="36" t="s">
-        <v>63</v>
+      <c r="G12" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8764,8 +8764,8 @@
       <c r="F13" s="35" t="s">
         <v>294</v>
       </c>
-      <c r="G13" s="36" t="s">
-        <v>63</v>
+      <c r="G13" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8787,8 +8787,8 @@
       <c r="F14" s="35" t="s">
         <v>297</v>
       </c>
-      <c r="G14" s="36" t="s">
-        <v>63</v>
+      <c r="G14" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8810,8 +8810,8 @@
       <c r="F15" s="31" t="s">
         <v>300</v>
       </c>
-      <c r="G15" s="32" t="s">
-        <v>63</v>
+      <c r="G15" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8833,8 +8833,8 @@
       <c r="F16" s="31" t="s">
         <v>303</v>
       </c>
-      <c r="G16" s="32" t="s">
-        <v>63</v>
+      <c r="G16" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8856,8 +8856,8 @@
       <c r="F17" s="31" t="s">
         <v>306</v>
       </c>
-      <c r="G17" s="32" t="s">
-        <v>63</v>
+      <c r="G17" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8879,8 +8879,8 @@
       <c r="F18" s="31" t="s">
         <v>309</v>
       </c>
-      <c r="G18" s="32" t="s">
-        <v>63</v>
+      <c r="G18" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8902,8 +8902,8 @@
       <c r="F19" s="31" t="s">
         <v>312</v>
       </c>
-      <c r="G19" s="32" t="s">
-        <v>63</v>
+      <c r="G19" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8925,8 +8925,8 @@
       <c r="F20" s="31" t="s">
         <v>315</v>
       </c>
-      <c r="G20" s="32" t="s">
-        <v>63</v>
+      <c r="G20" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8948,8 +8948,8 @@
       <c r="F21" s="31" t="s">
         <v>318</v>
       </c>
-      <c r="G21" s="32" t="s">
-        <v>63</v>
+      <c r="G21" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8971,8 +8971,8 @@
       <c r="F22" s="31" t="s">
         <v>321</v>
       </c>
-      <c r="G22" s="32" t="s">
-        <v>63</v>
+      <c r="G22" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8994,8 +8994,8 @@
       <c r="F23" s="31" t="s">
         <v>324</v>
       </c>
-      <c r="G23" s="32" t="s">
-        <v>63</v>
+      <c r="G23" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9108,8 +9108,8 @@
       <c r="F4" s="31" t="s">
         <v>329</v>
       </c>
-      <c r="G4" s="32" t="s">
-        <v>63</v>
+      <c r="G4" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9131,8 +9131,8 @@
       <c r="F5" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="G5" s="36" t="s">
-        <v>63</v>
+      <c r="G5" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9154,8 +9154,8 @@
       <c r="F6" s="31" t="s">
         <v>335</v>
       </c>
-      <c r="G6" s="32" t="s">
-        <v>63</v>
+      <c r="G6" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9177,8 +9177,8 @@
       <c r="F7" s="31" t="s">
         <v>338</v>
       </c>
-      <c r="G7" s="32" t="s">
-        <v>63</v>
+      <c r="G7" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9200,8 +9200,8 @@
       <c r="F8" s="31" t="s">
         <v>341</v>
       </c>
-      <c r="G8" s="32" t="s">
-        <v>63</v>
+      <c r="G8" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9223,8 +9223,8 @@
       <c r="F9" s="31" t="s">
         <v>344</v>
       </c>
-      <c r="G9" s="32" t="s">
-        <v>63</v>
+      <c r="G9" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9246,8 +9246,8 @@
       <c r="F10" s="31" t="s">
         <v>347</v>
       </c>
-      <c r="G10" s="32" t="s">
-        <v>63</v>
+      <c r="G10" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9269,8 +9269,8 @@
       <c r="F11" s="31" t="s">
         <v>350</v>
       </c>
-      <c r="G11" s="32" t="s">
-        <v>63</v>
+      <c r="G11" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9292,8 +9292,8 @@
       <c r="F12" s="31" t="s">
         <v>353</v>
       </c>
-      <c r="G12" s="32" t="s">
-        <v>63</v>
+      <c r="G12" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9315,8 +9315,8 @@
       <c r="F13" s="31" t="s">
         <v>356</v>
       </c>
-      <c r="G13" s="32" t="s">
-        <v>63</v>
+      <c r="G13" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9338,8 +9338,8 @@
       <c r="F14" s="35" t="s">
         <v>359</v>
       </c>
-      <c r="G14" s="36" t="s">
-        <v>63</v>
+      <c r="G14" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9361,8 +9361,8 @@
       <c r="F15" s="31" t="s">
         <v>362</v>
       </c>
-      <c r="G15" s="32" t="s">
-        <v>63</v>
+      <c r="G15" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9384,8 +9384,8 @@
       <c r="F16" s="31" t="s">
         <v>365</v>
       </c>
-      <c r="G16" s="32" t="s">
-        <v>63</v>
+      <c r="G16" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9407,8 +9407,8 @@
       <c r="F17" s="35" t="s">
         <v>368</v>
       </c>
-      <c r="G17" s="36" t="s">
-        <v>63</v>
+      <c r="G17" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9430,8 +9430,8 @@
       <c r="F18" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="G18" s="36" t="s">
-        <v>63</v>
+      <c r="G18" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9453,8 +9453,8 @@
       <c r="F19" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="G19" s="32" t="s">
-        <v>63</v>
+      <c r="G19" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9476,8 +9476,8 @@
       <c r="F20" s="31" t="s">
         <v>377</v>
       </c>
-      <c r="G20" s="32" t="s">
-        <v>63</v>
+      <c r="G20" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9499,8 +9499,8 @@
       <c r="F21" s="31" t="s">
         <v>315</v>
       </c>
-      <c r="G21" s="32" t="s">
-        <v>63</v>
+      <c r="G21" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9522,8 +9522,8 @@
       <c r="F22" s="31" t="s">
         <v>382</v>
       </c>
-      <c r="G22" s="32" t="s">
-        <v>63</v>
+      <c r="G22" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9545,8 +9545,8 @@
       <c r="F23" s="31" t="s">
         <v>385</v>
       </c>
-      <c r="G23" s="32" t="s">
-        <v>63</v>
+      <c r="G23" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9659,8 +9659,8 @@
       <c r="F4" s="26" t="s">
         <v>390</v>
       </c>
-      <c r="G4" s="27" t="s">
-        <v>63</v>
+      <c r="G4" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9682,8 +9682,8 @@
       <c r="F5" s="31" t="s">
         <v>393</v>
       </c>
-      <c r="G5" s="32" t="s">
-        <v>63</v>
+      <c r="G5" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9705,8 +9705,8 @@
       <c r="F6" s="31" t="s">
         <v>396</v>
       </c>
-      <c r="G6" s="32" t="s">
-        <v>63</v>
+      <c r="G6" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9728,8 +9728,8 @@
       <c r="F7" s="31" t="s">
         <v>399</v>
       </c>
-      <c r="G7" s="32" t="s">
-        <v>63</v>
+      <c r="G7" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9751,8 +9751,8 @@
       <c r="F8" s="31" t="s">
         <v>402</v>
       </c>
-      <c r="G8" s="32" t="s">
-        <v>63</v>
+      <c r="G8" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9774,8 +9774,8 @@
       <c r="F9" s="31" t="s">
         <v>405</v>
       </c>
-      <c r="G9" s="32" t="s">
-        <v>63</v>
+      <c r="G9" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9797,8 +9797,8 @@
       <c r="F10" s="35" t="s">
         <v>408</v>
       </c>
-      <c r="G10" s="36" t="s">
-        <v>63</v>
+      <c r="G10" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9820,8 +9820,8 @@
       <c r="F11" s="35" t="s">
         <v>411</v>
       </c>
-      <c r="G11" s="36" t="s">
-        <v>63</v>
+      <c r="G11" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9843,8 +9843,8 @@
       <c r="F12" s="35" t="s">
         <v>412</v>
       </c>
-      <c r="G12" s="36" t="s">
-        <v>63</v>
+      <c r="G12" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9866,8 +9866,8 @@
       <c r="F13" s="35" t="s">
         <v>415</v>
       </c>
-      <c r="G13" s="36" t="s">
-        <v>63</v>
+      <c r="G13" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9889,8 +9889,8 @@
       <c r="F14" s="35" t="s">
         <v>418</v>
       </c>
-      <c r="G14" s="36" t="s">
-        <v>63</v>
+      <c r="G14" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9912,8 +9912,8 @@
       <c r="F15" s="35" t="s">
         <v>419</v>
       </c>
-      <c r="G15" s="36" t="s">
-        <v>63</v>
+      <c r="G15" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9935,8 +9935,8 @@
       <c r="F16" s="35" t="s">
         <v>422</v>
       </c>
-      <c r="G16" s="36" t="s">
-        <v>63</v>
+      <c r="G16" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9958,8 +9958,8 @@
       <c r="F17" s="35" t="s">
         <v>425</v>
       </c>
-      <c r="G17" s="36" t="s">
-        <v>63</v>
+      <c r="G17" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9981,8 +9981,8 @@
       <c r="F18" s="31" t="s">
         <v>428</v>
       </c>
-      <c r="G18" s="32" t="s">
-        <v>63</v>
+      <c r="G18" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10004,8 +10004,8 @@
       <c r="F19" s="31" t="s">
         <v>431</v>
       </c>
-      <c r="G19" s="32" t="s">
-        <v>63</v>
+      <c r="G19" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10027,8 +10027,8 @@
       <c r="F20" s="31" t="s">
         <v>434</v>
       </c>
-      <c r="G20" s="32" t="s">
-        <v>63</v>
+      <c r="G20" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10050,8 +10050,8 @@
       <c r="F21" s="31" t="s">
         <v>437</v>
       </c>
-      <c r="G21" s="32" t="s">
-        <v>63</v>
+      <c r="G21" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10073,8 +10073,8 @@
       <c r="F22" s="31" t="s">
         <v>440</v>
       </c>
-      <c r="G22" s="32" t="s">
-        <v>63</v>
+      <c r="G22" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10096,8 +10096,8 @@
       <c r="F23" s="31" t="s">
         <v>443</v>
       </c>
-      <c r="G23" s="32" t="s">
-        <v>63</v>
+      <c r="G23" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10119,8 +10119,8 @@
       <c r="F24" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="G24" s="36" t="s">
-        <v>63</v>
+      <c r="G24" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10142,8 +10142,8 @@
       <c r="F25" s="31" t="s">
         <v>447</v>
       </c>
-      <c r="G25" s="32" t="s">
-        <v>63</v>
+      <c r="G25" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10165,8 +10165,8 @@
       <c r="F26" s="31" t="s">
         <v>450</v>
       </c>
-      <c r="G26" s="32" t="s">
-        <v>63</v>
+      <c r="G26" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10188,8 +10188,8 @@
       <c r="F27" s="31" t="s">
         <v>402</v>
       </c>
-      <c r="G27" s="32" t="s">
-        <v>63</v>
+      <c r="G27" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10211,8 +10211,8 @@
       <c r="F28" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="G28" s="36" t="s">
-        <v>63</v>
+      <c r="G28" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10234,8 +10234,8 @@
       <c r="F29" s="31" t="s">
         <v>458</v>
       </c>
-      <c r="G29" s="32" t="s">
-        <v>63</v>
+      <c r="G29" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10257,8 +10257,8 @@
       <c r="F30" s="35" t="s">
         <v>461</v>
       </c>
-      <c r="G30" s="36" t="s">
-        <v>63</v>
+      <c r="G30" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10280,8 +10280,8 @@
       <c r="F31" s="35" t="s">
         <v>464</v>
       </c>
-      <c r="G31" s="36" t="s">
-        <v>63</v>
+      <c r="G31" s="64" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
